--- a/output/projects/Norsjo/excel/ArbetsExcel_Norsjo_byggd.xlsx
+++ b/output/projects/Norsjo/excel/ArbetsExcel_Norsjo_byggd.xlsx
@@ -10,10 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxa_från_edp" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Körningsinfo" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxa_Förslag" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regelspårning" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Standard_Standard Avfall" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Standard_Standard Slam" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Standard_Standard ÅVS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Avviker_Standard" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regelspårning" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Standard_Standard Avfall" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Standard_Standard Slam" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Standard_Standard ÅVS" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -600,7 +601,28 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RegelsparningTable" displayName="RegelsparningTable" ref="A6:J7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EdpAvvikerStandardTable" displayName="EdpAvvikerStandardTable" ref="A6:L7" headerRowCount="1">
+  <autoFilter ref="A6:L7"/>
+  <tableColumns count="12">
+    <tableColumn id="1" name="Kommun"/>
+    <tableColumn id="2" name="EDP taxekod"/>
+    <tableColumn id="3" name="EDP benämning"/>
+    <tableColumn id="4" name="EDP faktor"/>
+    <tableColumn id="5" name="EDP taxedel"/>
+    <tableColumn id="6" name="Standard taxekod"/>
+    <tableColumn id="7" name="Standard benämning"/>
+    <tableColumn id="8" name="Standard faktor"/>
+    <tableColumn id="9" name="Standard taxedel"/>
+    <tableColumn id="10" name="Avvikelse"/>
+    <tableColumn id="11" name="Rekommendation"/>
+    <tableColumn id="12" name="Status"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RegelsparningTable" displayName="RegelsparningTable" ref="A6:J7" headerRowCount="1">
   <autoFilter ref="A6:J7"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Kommun"/>
@@ -28406,7 +28428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -28474,36 +28496,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Standardtaxor</t>
+          <t>EDP-regel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Inkluderade som referensflikar om standardtaxefilen finns</t>
+          <t>Taxor i Taxa_från_edp är fasta och ändras inte automatiskt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Taxa_Förslag</t>
+          <t>Standardtaxor</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ingår i alla outputfiler för föreslagna saknade taxekoder</t>
+          <t>Inkluderade som referensflikar om standardtaxefilen finns</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Taxa_Förslag</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ingår för föreslagna saknade taxekoder</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EDP_Avviker_Standard</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ingår för avvikelser mot standardtaxor</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Regelspårning</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ingår i alla outputfiler för spårbarhet av beslut/regler</t>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ingår för spårbarhet av beslut/regler</t>
         </is>
       </c>
     </row>
@@ -28677,6 +28723,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="54" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>EDP Export avviker från standardtaxa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Syfte</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Visar avvikelser mot standardtaxor. Befintlig Taxa_från_edp är fast och ändras aldrig automatiskt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Kommun</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Källa</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>EDP-export: data\edp_exports\Norsjo.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Kommun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>EDP taxekod</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>EDP benämning</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>EDP faktor</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>EDP taxedel</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Standard taxekod</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Standard benämning</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Standard faktor</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Standard taxedel</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Avvikelse</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Rekommendation</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Granska manuellt. Ändra inte befintlig EDP automatiskt.</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -28686,7 +28894,7 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
@@ -28808,7 +29016,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Taxakod får endast sättas från säker EDP-match eller markerat förslag.</t>
+          <t>Befintlig Taxa_från_edp är fast. Standardtaxor får endast ge förslag/avvikelse.</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -28835,7 +29043,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -42275,7 +42483,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -45948,7 +46156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/output/projects/Norsjo/excel/ArbetsExcel_Norsjo_byggd.xlsx
+++ b/output/projects/Norsjo/excel/ArbetsExcel_Norsjo_byggd.xlsx
@@ -1079,8 +1079,6 @@
           <t>140L kärl - viktavgift matavfall</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -1096,7 +1094,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>-</t>
@@ -1154,8 +1151,6 @@
           <t>Överviktsavgift för vikt över 60 kg, matavfall</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>3.68</t>
@@ -1171,7 +1166,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>-</t>
@@ -1229,8 +1223,6 @@
           <t>140-370L kärl - viktavgift restavfall</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -1246,7 +1238,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>-</t>
@@ -1304,8 +1295,6 @@
           <t>Överviktsavgift för vikt över 60 kg, restavfall</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>7.36</t>
@@ -1321,7 +1310,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>-</t>
@@ -1379,8 +1367,6 @@
           <t>660L kärl - viktavgift restavfall</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -1396,7 +1382,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>-</t>
@@ -1454,8 +1439,6 @@
           <t>Överviktsavgift för vikt över 100 kg, restavfall</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>7.36</t>
@@ -1471,7 +1454,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>-</t>
@@ -1529,8 +1511,6 @@
           <t>Absorberingsmedel, filtermaterial</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>25.0</t>
@@ -1546,7 +1526,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>-</t>
@@ -1604,8 +1583,6 @@
           <t>Aerosoler, ej bekämpningsmedel</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>40.0</t>
@@ -1621,7 +1598,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>-</t>
@@ -1679,8 +1655,6 @@
           <t>Aerosoler, färg</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>20.0</t>
@@ -1696,7 +1670,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>-</t>
@@ -1754,8 +1727,6 @@
           <t>Aerosoler, härdare med isocyanater, bekämpningsmedel</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>40.0</t>
@@ -1771,7 +1742,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>-</t>
@@ -1829,8 +1799,6 @@
           <t>Ammoniak</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>25.0</t>
@@ -1846,7 +1814,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>-</t>
@@ -1904,8 +1871,6 @@
           <t>Asbest max 15kg</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>1000.0</t>
@@ -1921,7 +1886,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>-</t>
@@ -1979,8 +1943,6 @@
           <t>Asbest, emballeringskostnad vid dåligt emballage</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>250.0</t>
@@ -1996,7 +1958,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>-</t>
@@ -2054,8 +2015,6 @@
           <t>ÅVC-abonnemang nivå 1 – ej miljöfarligt avfall</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>2000.0</t>
@@ -2071,7 +2030,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>-</t>
@@ -2082,7 +2040,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2125,8 +2082,6 @@
           <t>ÅVC-abonnemang nivå 2 – med miljöfarligt avfall</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>4000.0</t>
@@ -2142,7 +2097,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>-</t>
@@ -2153,7 +2107,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2196,16 +2149,11 @@
           <t>Avslut av tjänst</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>-</t>
@@ -2243,7 +2191,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>1</t>
@@ -2259,8 +2206,6 @@
           <t>Avstängning/strypning av vattentillförsel</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>960.0</t>
@@ -2276,7 +2221,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>-</t>
@@ -2334,8 +2278,6 @@
           <t>Tömning BDT-vatten, 0-3 m³</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>1320.0</t>
@@ -2351,7 +2293,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>-</t>
@@ -2409,8 +2350,6 @@
           <t>BDT 0-3 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2426,7 +2365,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>-</t>
@@ -2484,8 +2422,6 @@
           <t>BDT 0-3 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2501,7 +2437,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>-</t>
@@ -2559,8 +2494,6 @@
           <t>BDT över 3 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2576,7 +2509,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>-</t>
@@ -2634,8 +2566,6 @@
           <t>BDT över 3 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2651,7 +2581,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>-</t>
@@ -2709,8 +2638,6 @@
           <t>Bekämpningsmedel, ej kvicksilverhaltiga</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>35.0</t>
@@ -2726,7 +2653,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>-</t>
@@ -2784,8 +2710,6 @@
           <t>Bensinrester</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>10.0</t>
@@ -2801,7 +2725,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>-</t>
@@ -2859,8 +2782,6 @@
           <t>Mottagningsavgift extrasäck till ÅVC</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>240.0</t>
@@ -2876,7 +2797,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>-</t>
@@ -2934,8 +2854,6 @@
           <t>Brandsläckare</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>25.0</t>
@@ -2951,7 +2869,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>-</t>
@@ -3009,8 +2926,6 @@
           <t>Budad hämtning, bygg- rivningsavfall. Pris per m³</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -3026,7 +2941,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>-</t>
@@ -3084,8 +2998,6 @@
           <t>Tömning slam, brunn 0-3 m³</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>1320.0</t>
@@ -3101,7 +3013,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>-</t>
@@ -3159,8 +3070,6 @@
           <t>Brunn 0-3 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3176,7 +3085,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>X</t>
@@ -3234,8 +3142,6 @@
           <t>Brunn 0-3 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3251,7 +3157,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>-</t>
@@ -3309,8 +3214,6 @@
           <t>Brunn 0-3 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3326,7 +3229,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>-</t>
@@ -3384,8 +3286,6 @@
           <t>Tömning slam, brunn 3,1-6 m³</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>2280.0</t>
@@ -3401,7 +3301,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>-</t>
@@ -3459,8 +3358,6 @@
           <t>Brunn 3,1-6 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3476,7 +3373,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
           <t>-</t>
@@ -3534,8 +3430,6 @@
           <t>Brunn 3,1-6 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3551,7 +3445,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>-</t>
@@ -3609,8 +3502,6 @@
           <t>Brunn 0-3 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3626,7 +3517,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>-</t>
@@ -3684,16 +3574,11 @@
           <t>Brunn 6,1-9 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>-</t>
@@ -3751,8 +3636,6 @@
           <t>Tömning slam, brunn över 6,1 m³</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>3240.0</t>
@@ -3768,7 +3651,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>-</t>
@@ -3826,8 +3708,6 @@
           <t>Brunn 6,1-9 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3843,7 +3723,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>-</t>
@@ -3901,8 +3780,6 @@
           <t>Brunn 6,1-9 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3918,7 +3795,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>-</t>
@@ -3976,8 +3852,6 @@
           <t>Brunn över 9 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3993,7 +3867,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>-</t>
@@ -4051,8 +3924,6 @@
           <t>Brunn över 9 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4068,7 +3939,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>-</t>
@@ -4126,8 +3996,6 @@
           <t>Bromsvätska</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>25.0</t>
@@ -4143,7 +4011,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>-</t>
@@ -4201,8 +4068,6 @@
           <t>Brännbart, sorterat &lt;20 x 20 x 80 cm</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>600.0</t>
@@ -4218,7 +4083,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>-</t>
@@ -4276,8 +4140,6 @@
           <t>Brännbart, överstort</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>650.0</t>
@@ -4293,7 +4155,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
           <t>-</t>
@@ -4351,8 +4212,6 @@
           <t>Budning av kommunalt avfall, framkörningsavgift</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>1600.0</t>
@@ -4368,7 +4227,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>-</t>
@@ -4426,8 +4284,6 @@
           <t>Byggvatten, Rörlig avgift, förbrukning per m³</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>30.4</t>
@@ -4443,7 +4299,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>-</t>
@@ -4454,7 +4309,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4497,8 +4351,6 @@
           <t>Byggvatten, Rörlig avgift, uppsk. förbrukning per m³</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>30.4</t>
@@ -4514,7 +4366,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>-</t>
@@ -4525,7 +4376,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4568,8 +4418,6 @@
           <t>Bygg- och rivningsavfall, plast</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>600.0</t>
@@ -4585,7 +4433,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>-</t>
@@ -4643,8 +4490,6 @@
           <t>Bygg- och rivningsavfall, trä</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>650.0</t>
@@ -4660,7 +4505,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>-</t>
@@ -4718,8 +4562,6 @@
           <t>Tjänsttaxa container för matavfall</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4735,7 +4577,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>-</t>
@@ -4793,8 +4634,6 @@
           <t>Tjänsttaxa container för restavfall</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4810,7 +4649,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>-</t>
@@ -4868,8 +4706,6 @@
           <t>Cytotoxiska/Cytostatika</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>60.0</t>
@@ -4885,7 +4721,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>-</t>
@@ -4943,8 +4778,6 @@
           <t>Deponirest utsorterad/ej brännbart</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>800.0</t>
@@ -4960,7 +4793,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>-</t>
@@ -5018,8 +4850,6 @@
           <t>Brunn 0-3 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5035,7 +4865,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>-</t>
@@ -5093,8 +4922,6 @@
           <t>Felaktigt/farligt avfall ej klassat, pris per tillfälle</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>1000.0</t>
@@ -5110,7 +4937,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>-</t>
@@ -5168,8 +4994,6 @@
           <t>Ej specificerat farligt avfall</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>1000.0</t>
@@ -5185,7 +5009,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>-</t>
@@ -5243,8 +5066,6 @@
           <t>Elektronikavfall, ej producentansvar</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5260,7 +5081,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>-</t>
@@ -5318,8 +5138,6 @@
           <t>Evenemang framkörningsavgift</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -5335,7 +5153,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>-</t>
@@ -5393,8 +5210,6 @@
           <t>Evenemangskärl 140 L, matavfall</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>96.0</t>
@@ -5410,7 +5225,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>-</t>
@@ -5468,8 +5282,6 @@
           <t>Evenemangskärl 190 L, restavfall</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>96.0</t>
@@ -5485,7 +5297,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
           <t>-</t>
@@ -5543,8 +5354,6 @@
           <t>Evenemangskärl 370 L, restavfall</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>120.0</t>
@@ -5560,7 +5369,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
           <t>-</t>
@@ -5618,8 +5426,6 @@
           <t>Evenemangskärl 660 L, restavfall</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>184.0</t>
@@ -5635,7 +5441,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>-</t>
@@ -5693,8 +5498,6 @@
           <t>Tjänsttaxa för tillfälliga evenemangskärl</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>200.0</t>
@@ -5710,7 +5513,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
           <t>-</t>
@@ -5768,8 +5570,6 @@
           <t>Fast avgift, vatten/spillvatten</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>656.0</t>
@@ -5785,7 +5585,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
           <t>-</t>
@@ -5796,7 +5595,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5839,8 +5637,6 @@
           <t>Budning av kommunalt avfall, framkörningsavgift</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>320.0</t>
@@ -5856,7 +5652,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
           <t>-</t>
@@ -5914,8 +5709,6 @@
           <t>Tjänsttaxa för farligt avfall</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5931,7 +5724,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
           <t>-</t>
@@ -5989,8 +5781,6 @@
           <t>Budning av farligt avfall per m³</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>3840.0</t>
@@ -6006,7 +5796,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
           <t>-</t>
@@ -6064,8 +5853,6 @@
           <t>Fast oljeavfall</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>25.0</t>
@@ -6081,7 +5868,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
           <t>-</t>
@@ -6139,8 +5925,6 @@
           <t>Fast soda i små emballage</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>50.0</t>
@@ -6156,7 +5940,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
           <t>-</t>
@@ -6214,8 +5997,6 @@
           <t>Felsorteringsavgift</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>800.0</t>
@@ -6231,7 +6012,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
           <t>-</t>
@@ -6289,8 +6069,6 @@
           <t>Nyckelfob, engångskostnad</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>1200.0</t>
@@ -6306,7 +6084,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
           <t>-</t>
@@ -6364,8 +6141,6 @@
           <t>Avser fysisk nyckel för mat-och restavfall - Engångskostnad</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>1200.0</t>
@@ -6381,7 +6156,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
           <t>-</t>
@@ -6439,8 +6213,6 @@
           <t>Fosforfälla. Budning</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -6456,7 +6228,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
           <t>-</t>
@@ -6514,8 +6285,6 @@
           <t>Fosforfälla. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -6531,7 +6300,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
           <t>-</t>
@@ -6589,8 +6357,6 @@
           <t>Tömning och behandling fosforfilter 500-1000 kg</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>3840.0</t>
@@ -6606,7 +6372,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
           <t>-</t>
@@ -6664,8 +6429,6 @@
           <t>Tömning och behandling fosforfilter under 500 kg</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>2880.0</t>
@@ -6681,7 +6444,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
           <t>-</t>
@@ -6739,8 +6501,6 @@
           <t>Fotokemikalier</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>35.0</t>
@@ -6756,7 +6516,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
           <t>-</t>
@@ -6814,8 +6573,6 @@
           <t>Framkörningsavgift, hämtning av kommunalt avfall</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>1600.0</t>
@@ -6831,7 +6588,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr">
         <is>
           <t>-</t>
@@ -6889,8 +6645,6 @@
           <t>Färg ej konsumentförpackat</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>25.0</t>
@@ -6906,7 +6660,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
           <t>-</t>
@@ -6964,8 +6717,6 @@
           <t>Färg/lackavfall/lim lösningsbaserat</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>10.0</t>
@@ -6981,7 +6732,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
           <t>-</t>
@@ -7039,8 +6789,6 @@
           <t>Färg/lackavfall/lim vattenbaserat</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>10.0</t>
@@ -7056,7 +6804,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
           <t>-</t>
@@ -7094,7 +6841,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>1</t>
@@ -7110,8 +6856,6 @@
           <t>Förgävesbesök vid avtalad tid eller avisering</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>960.0</t>
@@ -7127,7 +6871,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
           <t>-</t>
@@ -7185,8 +6928,6 @@
           <t>Gasol, blå programmet</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>500.0</t>
@@ -7202,7 +6943,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
           <t>-</t>
@@ -7260,8 +7000,6 @@
           <t>Hämtningavgift gemensam uppsamlingsplats, eget kärl</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -7277,7 +7015,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
           <t>-</t>
@@ -7335,8 +7072,6 @@
           <t>Viktavgift rest- matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7352,7 +7087,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
           <t>-</t>
@@ -7410,8 +7144,6 @@
           <t>Extra Mobilnyckel till ÅVS</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -7427,7 +7159,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
           <t>-</t>
@@ -7438,7 +7169,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7481,8 +7211,6 @@
           <t>Gemensam uppsamlingsplats, mat- och restavfall</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
           <t>600.0</t>
@@ -7498,7 +7226,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
           <t>-</t>
@@ -7556,8 +7283,6 @@
           <t>Nyckelfob, engångskostnad</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>1200.0</t>
@@ -7573,7 +7298,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
           <t>-</t>
@@ -7584,7 +7308,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7627,8 +7350,6 @@
           <t>Gemensam uppsamlingsplats Förpackning, Flerbostadshus</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7644,7 +7365,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
           <t>-</t>
@@ -7702,8 +7422,6 @@
           <t>Mobilnyckel Gemensam uppsamlingsplats, mat- och restavfall</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7719,7 +7437,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
           <t>-</t>
@@ -7777,8 +7494,6 @@
           <t>Budad hämtning, grovavfall. Pris per m³</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -7794,7 +7509,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
           <t>-</t>
@@ -7852,8 +7566,6 @@
           <t>Tjänsttaxa för grovavfall</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7869,7 +7581,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
           <t>-</t>
@@ -7927,8 +7638,6 @@
           <t>Budning av grovavfall per m³</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -7944,7 +7653,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
           <t>-</t>
@@ -8002,8 +7710,6 @@
           <t>Grundavgift, del i flerbostadshus</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>640.0</t>
@@ -8019,7 +7725,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
           <t>-</t>
@@ -8077,8 +7782,6 @@
           <t>Grundavgift, fritidshus</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>1000.0</t>
@@ -8094,7 +7797,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
           <t>-</t>
@@ -8152,8 +7854,6 @@
           <t>Grundavgift, småhus 1- och 2 familjshus</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
           <t>1320.0</t>
@@ -8169,7 +7869,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
           <t>-</t>
@@ -8227,8 +7926,6 @@
           <t>Grundavgift, verksamheter</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>1000.0</t>
@@ -8244,7 +7941,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
           <t>-</t>
@@ -8302,8 +7998,6 @@
           <t>Halon gaser</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>160.0</t>
@@ -8319,7 +8013,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
           <t>-</t>
@@ -8377,8 +8070,6 @@
           <t>Hydraulslang</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>15.0</t>
@@ -8394,7 +8085,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
           <t>-</t>
@@ -8452,8 +8142,6 @@
           <t>Härdare</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
           <t>60.0</t>
@@ -8469,7 +8157,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
           <t>-</t>
@@ -8527,8 +8214,6 @@
           <t>Impregnerat trä, bygg- o rivningsavfall</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
           <t>400.0</t>
@@ -8544,7 +8229,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
           <t>-</t>
@@ -8602,8 +8286,6 @@
           <t>Invasiva växter från hushåll</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8619,7 +8301,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
           <t>-</t>
@@ -8677,8 +8358,6 @@
           <t>Invasiva växter från verksamheter</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
           <t>200.0</t>
@@ -8694,7 +8373,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
         <is>
           <t>-</t>
@@ -8752,8 +8430,6 @@
           <t>Kolsyrepatroner</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
           <t>40.0</t>
@@ -8769,7 +8445,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
           <t>-</t>
@@ -8827,8 +8502,6 @@
           <t>Tjänsttaxa kommunalt avfall</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8844,7 +8517,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
           <t>-</t>
@@ -8902,8 +8574,6 @@
           <t>Kvicksilverinstrument/komponenter</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
           <t>400.0</t>
@@ -8919,7 +8589,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
           <t>-</t>
@@ -8977,8 +8646,6 @@
           <t>Kyldiskar och större kylmöbler</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8994,7 +8661,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
           <t>-</t>
@@ -9052,8 +8718,6 @@
           <t>Kylmöbler, mindre (60 cm x 60 cm)</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -9069,7 +8733,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
           <t>-</t>
@@ -9127,8 +8790,6 @@
           <t>Kärl 140L, matavfall. Var 14:e dag</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -9144,7 +8805,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
         <is>
           <t>-</t>
@@ -9202,8 +8862,6 @@
           <t>Kärl 140L Viktavgift matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -9219,7 +8877,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
           <t>-</t>
@@ -9277,8 +8934,6 @@
           <t>Dragväg 1,5-10 meter</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -9294,7 +8949,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
           <t>-</t>
@@ -9352,8 +9006,6 @@
           <t>Dragväg 10,1-20 meter</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -9369,7 +9021,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
           <t>-</t>
@@ -9427,8 +9078,6 @@
           <t>Kärl 140L Överviktsavgift för vikt över 60 kg, matavfall</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -9444,7 +9093,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
           <t>-</t>
@@ -9502,8 +9150,6 @@
           <t>Kärl 140L, matavfall. Varje vecka</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
           <t>1240.0</t>
@@ -9519,7 +9165,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
           <t>-</t>
@@ -9577,8 +9222,6 @@
           <t>Kärl 140L Viktavgift matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -9594,7 +9237,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
           <t>-</t>
@@ -9652,8 +9294,6 @@
           <t>Dragväg 1,5-10 meter</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -9669,7 +9309,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
           <t>-</t>
@@ -9727,8 +9366,6 @@
           <t>Dragväg 10,1-20 meter</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -9744,7 +9381,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
           <t>-</t>
@@ -9802,8 +9438,6 @@
           <t>Kärl 140L Överviktsavgift för vikt över 60 kg, matavfall</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -9819,7 +9453,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr">
         <is>
           <t>-</t>
@@ -9877,8 +9510,6 @@
           <t>Kärl 120-190L extrakärl, rest/matavfall. Var 14:e dag</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
           <t>680.0</t>
@@ -9894,7 +9525,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr">
         <is>
           <t>-</t>
@@ -9952,8 +9582,6 @@
           <t>Viktavgift rest- matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
           <t>4.28</t>
@@ -9969,7 +9597,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
           <t>-</t>
@@ -10027,8 +9654,6 @@
           <t>Kärl 120-190L extrakärl, rest/matavfall. Var 14:e dag</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
           <t>680.0</t>
@@ -10044,7 +9669,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr">
         <is>
           <t>-</t>
@@ -10102,8 +9726,6 @@
           <t>Viktavgift rest- matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
           <t>4.28</t>
@@ -10119,7 +9741,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
         <is>
           <t>-</t>
@@ -10177,8 +9798,6 @@
           <t>Tvåfackskärl 240L, restavfall/kompost. Var 14:e dag</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
           <t>680.0</t>
@@ -10194,7 +9813,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
           <t>-</t>
@@ -10252,8 +9870,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
           <t>4.28</t>
@@ -10269,7 +9885,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr">
         <is>
           <t>-</t>
@@ -10327,8 +9942,6 @@
           <t>Tvåfackskärl 240L, restavfall/kompost. Var 14:e dag</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
           <t>680.0</t>
@@ -10344,7 +9957,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
           <t>-</t>
@@ -10402,8 +10014,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
           <t>4.28</t>
@@ -10419,7 +10029,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
           <t>-</t>
@@ -10477,8 +10086,6 @@
           <t>Tvåfackskärl 240L, rest/matavfall. Var 14:e dag</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>680.0</t>
@@ -10494,7 +10101,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
           <t>-</t>
@@ -10552,8 +10158,6 @@
           <t>Viktavgift rest- matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -10569,7 +10173,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
           <t>-</t>
@@ -10627,8 +10230,6 @@
           <t>Tvåfackskärl 240L, rest/matavfall. Var 14:e dag</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>680.0</t>
@@ -10644,7 +10245,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr">
         <is>
           <t>-</t>
@@ -10702,8 +10302,6 @@
           <t>Viktavgift rest- matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -10719,7 +10317,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr">
         <is>
           <t>-</t>
@@ -10777,8 +10374,6 @@
           <t>Tvåfackskärl 240L, rest/matavfall. Var 14:e dag</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>680.0</t>
@@ -10794,7 +10389,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
         <is>
           <t>-</t>
@@ -10852,8 +10446,6 @@
           <t>Viktavgift rest- matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -10869,7 +10461,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
           <t>-</t>
@@ -10927,8 +10518,6 @@
           <t>Dragväg 1,5-10 meter</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -10944,7 +10533,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
           <t>-</t>
@@ -11002,8 +10590,6 @@
           <t>Dragväg 10,1-20 meter</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11019,7 +10605,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
           <t>-</t>
@@ -11077,8 +10662,6 @@
           <t>Tvåfackskärl 240L, rest/matavfall. Varje vecka</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
           <t>1000.0</t>
@@ -11094,7 +10677,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr">
         <is>
           <t>-</t>
@@ -11152,8 +10734,6 @@
           <t>Viktavgift rest- matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11169,7 +10749,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
           <t>-</t>
@@ -11227,8 +10806,6 @@
           <t>Dragväg 1,5-10 meter</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11244,7 +10821,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
           <t>-</t>
@@ -11302,8 +10878,6 @@
           <t>Dragväg 10,1-20 meter</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11319,7 +10893,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
           <t>-</t>
@@ -11377,8 +10950,6 @@
           <t>Kärl 370L, restavfall. Var 14:e dag</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
           <t>800.0</t>
@@ -11394,7 +10965,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
           <t>-</t>
@@ -11452,8 +11022,6 @@
           <t>Kärl 370L 26V Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
           <t>4.28</t>
@@ -11469,7 +11037,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr">
         <is>
           <t>-</t>
@@ -11527,8 +11094,6 @@
           <t>Dragväg 1,5-10 meter</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11544,7 +11109,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
           <t>-</t>
@@ -11602,8 +11166,6 @@
           <t>Dragväg 10,1-20 meter</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11619,7 +11181,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr">
         <is>
           <t>-</t>
@@ -11677,8 +11238,6 @@
           <t>Kärl 370L 26V Överviktsavgift vikt över 60 kg, restavfall</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
           <t>6.4</t>
@@ -11694,7 +11253,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
         <is>
           <t>-</t>
@@ -11752,8 +11310,6 @@
           <t>Kärl 370L, restavfall. Varje vecka</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
           <t>2000.0</t>
@@ -11769,7 +11325,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr">
         <is>
           <t>-</t>
@@ -11827,8 +11382,6 @@
           <t>Kärl 370L 52V Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
           <t>4.28</t>
@@ -11844,7 +11397,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr">
         <is>
           <t>-</t>
@@ -11902,8 +11454,6 @@
           <t>Dragväg 1,5-10 meter</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11919,7 +11469,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr">
         <is>
           <t>-</t>
@@ -11977,8 +11526,6 @@
           <t>Dragväg 10,1-20 meter</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11994,7 +11541,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr">
         <is>
           <t>-</t>
@@ -12052,8 +11598,6 @@
           <t>Kärl 370L 52V Överviktsavgift vikt över 60 kg, restavfall</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
           <t>6.4</t>
@@ -12069,7 +11613,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
           <t>-</t>
@@ -12127,8 +11670,6 @@
           <t>Kärl 50l</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12144,7 +11685,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
           <t>-</t>
@@ -12202,8 +11742,6 @@
           <t>Viktavgift rest- matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12219,7 +11757,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr">
         <is>
           <t>-</t>
@@ -12277,8 +11814,6 @@
           <t>Kärl 660L, restavfall. Var 14:e dag</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
           <t>1680.0</t>
@@ -12294,7 +11829,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr">
         <is>
           <t>-</t>
@@ -12352,8 +11886,6 @@
           <t>Kärl 660L 26V Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
           <t>4.28</t>
@@ -12369,7 +11901,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr">
         <is>
           <t>-</t>
@@ -12427,8 +11958,6 @@
           <t>Dragväg 1,5-10 meter</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12444,7 +11973,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr">
         <is>
           <t>-</t>
@@ -12502,8 +12030,6 @@
           <t>Dragväg 10,1-20 meter</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12519,7 +12045,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr">
         <is>
           <t>-</t>
@@ -12577,8 +12102,6 @@
           <t>Kärl 660L 26V Överviktsavgift vikt över 100 kg, restavfall</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
           <t>8.0</t>
@@ -12594,7 +12117,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr">
         <is>
           <t>-</t>
@@ -12652,8 +12174,6 @@
           <t>Kärl 660L, restavfall. Varje vecka</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
           <t>3600.0</t>
@@ -12669,7 +12189,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr">
         <is>
           <t>-</t>
@@ -12727,8 +12246,6 @@
           <t>Kärl 660L 52V Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
           <t>4.28</t>
@@ -12744,7 +12261,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr">
         <is>
           <t>-</t>
@@ -12802,8 +12318,6 @@
           <t>Dragväg 1,5-10 meter</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12819,7 +12333,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr">
         <is>
           <t>-</t>
@@ -12877,8 +12390,6 @@
           <t>Dragväg 10,1-20 meter</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12894,7 +12405,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr">
         <is>
           <t>-</t>
@@ -12952,8 +12462,6 @@
           <t>Kärl 660L 52V Överviktsavgift vikt över 100 kg, restavfall</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
           <t>8.0</t>
@@ -12969,7 +12477,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr">
         <is>
           <t>-</t>
@@ -13027,8 +12534,6 @@
           <t>Byte/återtag av behållare en extra gång 140–240 liter</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
           <t>320.0</t>
@@ -13044,7 +12549,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr">
         <is>
           <t>-</t>
@@ -13102,8 +12606,6 @@
           <t>Byte/återtag av behållare en extra gång 370–660 liter</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
           <t>320.0</t>
@@ -13119,7 +12621,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr">
         <is>
           <t>-</t>
@@ -13177,8 +12678,6 @@
           <t>Ytterligare byte av kärl under kalenderåret</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -13194,7 +12693,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr">
         <is>
           <t>-</t>
@@ -13252,8 +12750,6 @@
           <t>Mottagningsavgift latrin till ÅVC</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
           <t>800.0</t>
@@ -13269,7 +12765,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr">
         <is>
           <t>-</t>
@@ -13327,8 +12822,6 @@
           <t>Budad hämtning, latrin i godkänd latrinbehållare</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
           <t>800.0</t>
@@ -13344,7 +12837,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr">
         <is>
           <t>-</t>
@@ -13402,8 +12894,6 @@
           <t>Köp av godkänd latrinbehållare</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
           <t>160.0</t>
@@ -13419,7 +12909,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr">
         <is>
           <t>-</t>
@@ -13477,8 +12966,6 @@
           <t>Lösningsmedel och träolja</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
           <t>10.0</t>
@@ -13494,7 +12981,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr">
         <is>
           <t>-</t>
@@ -13552,8 +13038,6 @@
           <t>Manuell sortering och hantering per person</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
           <t>500.0</t>
@@ -13569,7 +13053,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr">
         <is>
           <t>-</t>
@@ -13627,8 +13110,6 @@
           <t>Viktavgift matavfall</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -13644,7 +13125,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr">
         <is>
           <t>-</t>
@@ -13702,8 +13182,6 @@
           <t>Tjänsttaxa markbehållare för matavfall</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -13719,7 +13197,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr">
         <is>
           <t>-</t>
@@ -13777,8 +13254,6 @@
           <t>Viktavgift matavfall</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -13794,7 +13269,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr">
         <is>
           <t>-</t>
@@ -13852,8 +13326,6 @@
           <t>Tömning Markbehållare 1,6 m³, Matavfall</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
           <t>550.0</t>
@@ -13869,7 +13341,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr">
         <is>
           <t>-</t>
@@ -13927,8 +13398,6 @@
           <t>Tömning Markbehållare 1,6 m³, osorterat avfall</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
           <t>550.0</t>
@@ -13944,7 +13413,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr">
         <is>
           <t>-</t>
@@ -14002,8 +13470,6 @@
           <t>Tjänsttaxa underjordsbehållare för restavfall</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -14019,7 +13485,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr">
         <is>
           <t>-</t>
@@ -14077,8 +13542,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
           <t>4.28</t>
@@ -14094,7 +13557,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr">
         <is>
           <t>-</t>
@@ -14152,8 +13614,6 @@
           <t>Tömning Markbehållare 3,2 m³, Restavfall</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
           <t>550.0</t>
@@ -14169,7 +13629,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr">
         <is>
           <t>-</t>
@@ -14227,8 +13686,6 @@
           <t>Tömning Markbehållare 3,2 m³, osorterat avfall</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
           <t>550.0</t>
@@ -14244,7 +13701,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr">
         <is>
           <t>-</t>
@@ -14302,8 +13758,6 @@
           <t>Tjänsttaxa underjordsbehållare för matavfall</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -14319,7 +13773,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr">
         <is>
           <t>-</t>
@@ -14377,8 +13830,6 @@
           <t>Tömning Markbehållare 3,6 m³, osorterat avfall</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
           <t>400.0</t>
@@ -14394,7 +13845,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr">
         <is>
           <t>-</t>
@@ -14452,8 +13902,6 @@
           <t>Tömning Markbehållare 5 m³, osorterat avfall</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
           <t>400.0</t>
@@ -14469,7 +13917,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr">
         <is>
           <t>-</t>
@@ -14527,8 +13974,6 @@
           <t>Metallförpackningar, farlig fast/porös fyllning, tryckbehåll</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
           <t>40.0</t>
@@ -14544,7 +13989,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr">
         <is>
           <t>-</t>
@@ -14602,8 +14046,6 @@
           <t>Metallskrot, rent</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -14619,7 +14061,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr">
         <is>
           <t>-</t>
@@ -14677,16 +14118,11 @@
           <t>Miljövagn</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr">
         <is>
           <t>-</t>
@@ -14744,8 +14180,6 @@
           <t>Mobilnyckel Gemensam uppsamlingsplats, mat- och restavfall</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -14761,7 +14195,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr">
         <is>
           <t>-</t>
@@ -14819,8 +14252,6 @@
           <t>Extra mobilnyckel</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -14836,7 +14267,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr">
         <is>
           <t>-</t>
@@ -14894,8 +14324,6 @@
           <t>Minireningsverk 0-3 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
           <t>1320.0</t>
@@ -14911,7 +14339,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr">
         <is>
           <t>-</t>
@@ -14969,8 +14396,6 @@
           <t>Minireningsverk 0-3 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
           <t>1320.0</t>
@@ -14986,7 +14411,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr">
         <is>
           <t>-</t>
@@ -15044,8 +14468,6 @@
           <t>Minireningsverk 3,1-6 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
           <t>2280.0</t>
@@ -15061,7 +14483,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr">
         <is>
           <t>-</t>
@@ -15119,8 +14540,6 @@
           <t>Minireningsverk 3,1-6 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
           <t>2280.0</t>
@@ -15136,7 +14555,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr">
         <is>
           <t>-</t>
@@ -15194,8 +14612,6 @@
           <t>Minireningsverk 6,1-9 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
           <t>3240.0</t>
@@ -15211,7 +14627,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr">
         <is>
           <t>-</t>
@@ -15269,8 +14684,6 @@
           <t>Minireningsverk 6,1-9 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
           <t>3240.0</t>
@@ -15286,7 +14699,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr">
         <is>
           <t>-</t>
@@ -15344,8 +14756,6 @@
           <t>Minireningsverk över 9 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>3240.0</t>
@@ -15361,7 +14771,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr">
         <is>
           <t>-</t>
@@ -15419,8 +14828,6 @@
           <t>Minireningsverk över 9 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
           <t>3240.0</t>
@@ -15436,7 +14843,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr">
         <is>
           <t>-</t>
@@ -15474,7 +14880,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
           <t>1</t>
@@ -15490,8 +14895,6 @@
           <t>Nedtagning VA-mätare</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
           <t>960.0</t>
@@ -15507,7 +14910,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr">
         <is>
           <t>-</t>
@@ -15565,8 +14967,6 @@
           <t>Tjänsttaxa för ny tjänst Mat/Rest</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15582,7 +14982,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr">
         <is>
           <t>-</t>
@@ -15640,8 +15039,6 @@
           <t>Tjänsttaxa för ny tjänst matavfall</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15657,7 +15054,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr">
         <is>
           <t>-</t>
@@ -15715,8 +15111,6 @@
           <t>Tjänsttaxa för ny tjänst matavfall</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15732,7 +15126,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr">
         <is>
           <t>-</t>
@@ -15790,8 +15183,6 @@
           <t>Tjänsttaxa för ny tjänst osorterat avfall</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15807,7 +15198,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr">
         <is>
           <t>-</t>
@@ -15865,8 +15255,6 @@
           <t>Tjänsttaxa för ny tjänst osorterat avfall</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15882,7 +15270,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr">
         <is>
           <t>-</t>
@@ -15940,8 +15327,6 @@
           <t>Tjänsttaxa för ny tjänst restavfall</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15957,7 +15342,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr">
         <is>
           <t>-</t>
@@ -16015,8 +15399,6 @@
           <t>Tjänsttaxa för ny tjänst restavfall</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -16032,7 +15414,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr">
         <is>
           <t>-</t>
@@ -16090,8 +15471,6 @@
           <t>Tjänsttaxa för ny tjänst matavfall</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -16107,7 +15486,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr">
         <is>
           <t>-</t>
@@ -16165,8 +15543,6 @@
           <t>Oljefilter</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
           <t>10.0</t>
@@ -16182,7 +15558,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr">
         <is>
           <t>-</t>
@@ -16240,8 +15615,6 @@
           <t>Orderrad för ändrat antal. Hemtagning</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -16257,7 +15630,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr">
         <is>
           <t>-</t>
@@ -16315,8 +15687,6 @@
           <t>Orderrad för ändrat antal kärl, utsättning</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -16332,7 +15702,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr">
         <is>
           <t>-</t>
@@ -16390,8 +15759,6 @@
           <t>Orderrad för tömningsfrekvensbyte</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -16407,7 +15774,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr">
         <is>
           <t>-</t>
@@ -16465,8 +15831,6 @@
           <t>Orderrad för kärlbyte storlek, utsättning samt hemtagning</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -16482,7 +15846,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr">
         <is>
           <t>-</t>
@@ -16540,8 +15903,6 @@
           <t>Orderrad för ny tjänst, utsättning</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -16557,7 +15918,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr">
         <is>
           <t>-</t>
@@ -16615,8 +15975,6 @@
           <t>Orderrad för trasigt kärl. Laga/byta</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -16632,7 +15990,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr">
         <is>
           <t>-</t>
@@ -16670,7 +16027,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
           <t>1</t>
@@ -16686,8 +16042,6 @@
           <t>Påsläpp av vattentillförsel</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
           <t>960.0</t>
@@ -16703,7 +16057,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr">
         <is>
           <t>-</t>
@@ -16761,8 +16114,6 @@
           <t>Kärl 660L Viktavgift restavfall kr/kg (period)</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
           <t>4.28</t>
@@ -16778,7 +16129,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr">
         <is>
           <t>-</t>
@@ -16816,7 +16166,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
           <t>1</t>
@@ -16832,16 +16181,11 @@
           <t>Reglering restbelopp tidigare faktura</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr">
         <is>
           <t>-</t>
@@ -16879,7 +16223,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
           <t>1</t>
@@ -16895,8 +16238,6 @@
           <t>Reglering tillgodo tidigare faktura</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
           <t>1.75</t>
@@ -16912,7 +16253,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr">
         <is>
           <t>-</t>
@@ -16970,8 +16310,6 @@
           <t>Rengöringsmedel samt bilvårdsprodukter</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
           <t>25.0</t>
@@ -16987,7 +16325,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr">
         <is>
           <t>-</t>
@@ -17045,8 +16382,6 @@
           <t>Viktavgift restavfall</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
           <t>4.28</t>
@@ -17062,7 +16397,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr">
         <is>
           <t>-</t>
@@ -17120,8 +16454,6 @@
           <t>Fast avgift spillvatten</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
           <t>807.84</t>
@@ -17137,7 +16469,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr">
         <is>
           <t>-</t>
@@ -17148,7 +16479,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -17191,8 +16521,6 @@
           <t>Förbrukningsavgift, spillvatten</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
           <t>19.17</t>
@@ -17208,7 +16536,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr">
         <is>
           <t>-</t>
@@ -17219,7 +16546,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -17262,8 +16588,6 @@
           <t>Fast avgift spillvatten</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
           <t>807.84</t>
@@ -17279,7 +16603,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr">
         <is>
           <t>-</t>
@@ -17290,7 +16613,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -17333,8 +16655,6 @@
           <t>Förbrukningsavgift, avlopp</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
           <t>19.17</t>
@@ -17350,7 +16670,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr">
         <is>
           <t>-</t>
@@ -17361,7 +16680,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -17404,8 +16722,6 @@
           <t>Avgift, per lägenhet</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
           <t>1178.3</t>
@@ -17421,7 +16737,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr">
         <is>
           <t>-</t>
@@ -17479,8 +16794,6 @@
           <t>Avgift per påbörjad 150-tal m² bruttoarea</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
           <t>1178.3</t>
@@ -17496,7 +16809,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr">
         <is>
           <t>-</t>
@@ -17554,8 +16866,6 @@
           <t>Tillägg för budning inom 48 timmar</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
           <t>2800.0</t>
@@ -17571,7 +16881,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr">
         <is>
           <t>-</t>
@@ -17629,8 +16938,6 @@
           <t>Tillägg för budning inom 7 dagar</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
           <t>2000.0</t>
@@ -17646,7 +16953,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr">
         <is>
           <t>-</t>
@@ -17704,8 +17010,6 @@
           <t>Tillägg budad tömning</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
           <t>2400.0</t>
@@ -17721,7 +17025,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr">
         <is>
           <t>-</t>
@@ -17779,8 +17082,6 @@
           <t>Framkörningsavgift vid ej genomförd tömning</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
           <t>1200.0</t>
@@ -17796,7 +17097,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr">
         <is>
           <t>-</t>
@@ -17854,8 +17154,6 @@
           <t>Tillägg över 3 m³</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
           <t>212.0</t>
@@ -17871,7 +17169,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr">
         <is>
           <t>-</t>
@@ -17929,8 +17226,6 @@
           <t>Tillägg för kubikmeter överstigande 9,1 m³</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
           <t>560.0</t>
@@ -17946,7 +17241,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr">
         <is>
           <t>-</t>
@@ -18004,8 +17298,6 @@
           <t>Tillägg om förändring av slamtömning inte meddelats</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
           <t>1200.0</t>
@@ -18021,7 +17313,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr">
         <is>
           <t>-</t>
@@ -18079,8 +17370,6 @@
           <t>Tömning slam samtida brunn/tank mindre än 5 m³</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
           <t>1320.0</t>
@@ -18096,7 +17385,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr">
         <is>
           <t>-</t>
@@ -18154,8 +17442,6 @@
           <t>Total slanglängd, 10-30 m</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
           <t>320.0</t>
@@ -18171,7 +17457,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr">
         <is>
           <t>-</t>
@@ -18229,8 +17514,6 @@
           <t>Total slanglängd, 30-40 m</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -18246,7 +17529,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr">
         <is>
           <t>-</t>
@@ -18304,8 +17586,6 @@
           <t>Total slanglängd, över 40 m</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
           <t>720.0</t>
@@ -18321,7 +17601,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr">
         <is>
           <t>-</t>
@@ -18379,8 +17658,6 @@
           <t>ENT Total slanglängd, 1-10 m</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
           <t>320.0</t>
@@ -18396,7 +17673,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr">
         <is>
           <t>-</t>
@@ -18454,8 +17730,6 @@
           <t>ENT Total slanglängd, 11-20 m</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
           <t>320.0</t>
@@ -18471,7 +17745,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr">
         <is>
           <t>-</t>
@@ -18529,8 +17802,6 @@
           <t>ENT Total slanglängd, 21-30 m</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -18546,7 +17817,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr">
         <is>
           <t>-</t>
@@ -18604,8 +17874,6 @@
           <t>ENT Total slanglängd, 31-40 m</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
           <t>720.0</t>
@@ -18621,7 +17889,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr">
         <is>
           <t>-</t>
@@ -18679,8 +17946,6 @@
           <t>ENT Total slanglängd, 41-50 m</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
           <t>1200.0</t>
@@ -18696,7 +17961,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr">
         <is>
           <t>-</t>
@@ -18754,8 +18018,6 @@
           <t>Total slanglängd 0-10 meter</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -18771,7 +18033,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr">
         <is>
           <t>-</t>
@@ -18829,8 +18090,6 @@
           <t>Total slanglängd 21-30 meter</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -18846,7 +18105,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr">
         <is>
           <t>-</t>
@@ -18904,8 +18162,6 @@
           <t>Total slanglängd 11-20 meter</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr"/>
-      <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
           <t>320.0</t>
@@ -18921,7 +18177,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr">
         <is>
           <t>-</t>
@@ -18979,8 +18234,6 @@
           <t>Total slanglängd 31-40 meter</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
           <t>720.0</t>
@@ -18996,7 +18249,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N242" t="inlineStr"/>
       <c r="O242" t="inlineStr">
         <is>
           <t>-</t>
@@ -19054,8 +18306,6 @@
           <t>Total slanglängd 41-50 meter</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
           <t>1200.0</t>
@@ -19071,7 +18321,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N243" t="inlineStr"/>
       <c r="O243" t="inlineStr">
         <is>
           <t>-</t>
@@ -19129,8 +18378,6 @@
           <t>Tillägg för specificerad inställelsetid för tömning</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
           <t>1200.0</t>
@@ -19146,7 +18393,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr">
         <is>
           <t>-</t>
@@ -19204,8 +18450,6 @@
           <t>Statistik vikt slam</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -19221,7 +18465,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr">
         <is>
           <t>-</t>
@@ -19279,8 +18522,6 @@
           <t>Tömning slam, sluten tank 0-3 m³</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
           <t>1320.0</t>
@@ -19296,7 +18537,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr">
         <is>
           <t>-</t>
@@ -19354,8 +18594,6 @@
           <t>Sluten tank 0-3 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr"/>
-      <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -19371,7 +18609,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr">
         <is>
           <t>-</t>
@@ -19429,8 +18666,6 @@
           <t>Sluten tank 0-3 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr"/>
-      <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -19446,7 +18681,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N248" t="inlineStr"/>
       <c r="O248" t="inlineStr">
         <is>
           <t>-</t>
@@ -19504,8 +18738,6 @@
           <t>Tömning slam, sluten tank 3,1-6 m³</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
           <t>2280.0</t>
@@ -19521,7 +18753,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr">
         <is>
           <t>-</t>
@@ -19579,8 +18810,6 @@
           <t>Sluten tank 3,1-6 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -19596,7 +18825,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N250" t="inlineStr"/>
       <c r="O250" t="inlineStr">
         <is>
           <t>-</t>
@@ -19654,8 +18882,6 @@
           <t>Sluten tank 3,1-6 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr"/>
-      <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -19671,7 +18897,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N251" t="inlineStr"/>
       <c r="O251" t="inlineStr">
         <is>
           <t>-</t>
@@ -19729,8 +18954,6 @@
           <t>Tömning slam, sluten tank över 6,1 m³</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
           <t>3240.0</t>
@@ -19746,7 +18969,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N252" t="inlineStr"/>
       <c r="O252" t="inlineStr">
         <is>
           <t>-</t>
@@ -19804,8 +19026,6 @@
           <t>Sluten tank 6,1-9 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr"/>
-      <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -19821,7 +19041,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N253" t="inlineStr"/>
       <c r="O253" t="inlineStr">
         <is>
           <t>-</t>
@@ -19879,8 +19098,6 @@
           <t>Sluten tank 6,1-9 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr"/>
-      <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -19896,7 +19113,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N254" t="inlineStr"/>
       <c r="O254" t="inlineStr">
         <is>
           <t>-</t>
@@ -19954,8 +19170,6 @@
           <t>Tömning av toalettvagnar/TC, spolbil</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr"/>
-      <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
           <t>2400.0</t>
@@ -19971,7 +19185,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N255" t="inlineStr"/>
       <c r="O255" t="inlineStr">
         <is>
           <t>-</t>
@@ -20029,8 +19242,6 @@
           <t>Tillägg lyft av tungt brunnslock över 15 kg</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr"/>
-      <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
           <t>760.0</t>
@@ -20046,7 +19257,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr">
         <is>
           <t>-</t>
@@ -20104,8 +19314,6 @@
           <t>Sluten tank över 9 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr"/>
-      <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -20121,7 +19329,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N257" t="inlineStr"/>
       <c r="O257" t="inlineStr">
         <is>
           <t>-</t>
@@ -20179,8 +19386,6 @@
           <t>Sluten tank över 9 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr"/>
-      <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -20196,7 +19401,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N258" t="inlineStr"/>
       <c r="O258" t="inlineStr">
         <is>
           <t>-</t>
@@ -20234,7 +19438,6 @@
           <t>RENH</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
           <t>1</t>
@@ -20250,16 +19453,11 @@
           <t>Sms till kund</t>
         </is>
       </c>
-      <c r="I259" t="inlineStr"/>
-      <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
       <c r="M259" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N259" t="inlineStr"/>
       <c r="O259" t="inlineStr">
         <is>
           <t>-</t>
@@ -20317,8 +19515,6 @@
           <t>Småkemikalier</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
           <t>100.0</t>
@@ -20334,7 +19530,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N260" t="inlineStr"/>
       <c r="O260" t="inlineStr">
         <is>
           <t>-</t>
@@ -20392,8 +19587,6 @@
           <t>Smörjfett/oljor</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr"/>
-      <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
           <t>25.0</t>
@@ -20409,7 +19602,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N261" t="inlineStr"/>
       <c r="O261" t="inlineStr">
         <is>
           <t>-</t>
@@ -20467,8 +19659,6 @@
           <t>Metallskrot, rent. Timtid</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr"/>
-      <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
           <t>500.0</t>
@@ -20484,7 +19674,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N262" t="inlineStr"/>
       <c r="O262" t="inlineStr">
         <is>
           <t>-</t>
@@ -20542,8 +19731,6 @@
           <t>Spackel och fönsterkitt</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr"/>
-      <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
           <t>25.0</t>
@@ -20559,7 +19746,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N263" t="inlineStr"/>
       <c r="O263" t="inlineStr">
         <is>
           <t>-</t>
@@ -20617,8 +19803,6 @@
           <t>Spillolja</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr"/>
-      <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
           <t>10.0</t>
@@ -20634,7 +19818,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N264" t="inlineStr"/>
       <c r="O264" t="inlineStr">
         <is>
           <t>-</t>
@@ -20692,8 +19875,6 @@
           <t>Fast avgift spillvatten</t>
         </is>
       </c>
-      <c r="I265" t="inlineStr"/>
-      <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
           <t>807.84</t>
@@ -20709,7 +19890,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N265" t="inlineStr"/>
       <c r="O265" t="inlineStr">
         <is>
           <t>-</t>
@@ -20720,7 +19900,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -20763,8 +19942,6 @@
           <t>Rörlig avgift, uppsk. förbrukning spillvatten</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr"/>
-      <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
           <t>19.17</t>
@@ -20780,7 +19957,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N266" t="inlineStr"/>
       <c r="O266" t="inlineStr">
         <is>
           <t>-</t>
@@ -20791,7 +19967,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -20834,8 +20009,6 @@
           <t>Fast avgift spillvatten</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr"/>
-      <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
           <t>807.84</t>
@@ -20851,7 +20024,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N267" t="inlineStr"/>
       <c r="O267" t="inlineStr">
         <is>
           <t>-</t>
@@ -20862,7 +20034,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -20905,8 +20076,6 @@
           <t>Rörlig avgift, uppsk. förbrukning spillvatten</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr"/>
-      <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
           <t>19.17</t>
@@ -20922,7 +20091,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N268" t="inlineStr"/>
       <c r="O268" t="inlineStr">
         <is>
           <t>-</t>
@@ -20933,7 +20101,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -20976,8 +20143,6 @@
           <t>Avgift, per lägenhet</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr"/>
-      <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
           <t>1178.3</t>
@@ -20993,7 +20158,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N269" t="inlineStr"/>
       <c r="O269" t="inlineStr">
         <is>
           <t>-</t>
@@ -21051,8 +20215,6 @@
           <t>Avgift per påbörjad 150-tal m² bruttoarea</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr"/>
-      <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
           <t>1178.3</t>
@@ -21068,7 +20230,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N270" t="inlineStr"/>
       <c r="O270" t="inlineStr">
         <is>
           <t>-</t>
@@ -21126,8 +20287,6 @@
           <t>Syror eller basiskt avfall</t>
         </is>
       </c>
-      <c r="I271" t="inlineStr"/>
-      <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
           <t>25.0</t>
@@ -21143,7 +20302,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N271" t="inlineStr"/>
       <c r="O271" t="inlineStr">
         <is>
           <t>-</t>
@@ -21201,8 +20359,6 @@
           <t>Budad hämtning, 140 L pappersäck matavfall</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
           <t>160.0</t>
@@ -21218,7 +20374,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N272" t="inlineStr"/>
       <c r="O272" t="inlineStr">
         <is>
           <t>-</t>
@@ -21276,8 +20431,6 @@
           <t>Budad hämtning, 160 L säck restavfall</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
           <t>160.0</t>
@@ -21293,7 +20446,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr">
         <is>
           <t>-</t>
@@ -21351,8 +20503,6 @@
           <t>Budad hämtning, trädgårdsavfall. Pris per säck</t>
         </is>
       </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -21368,7 +20518,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N274" t="inlineStr"/>
       <c r="O274" t="inlineStr">
         <is>
           <t>-</t>
@@ -21426,16 +20575,11 @@
           <t>240 l kärl/4 vecka test glas färgat ofärgat</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
       <c r="M275" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N275" t="inlineStr"/>
       <c r="O275" t="inlineStr">
         <is>
           <t>X</t>
@@ -21493,16 +20637,11 @@
           <t>240 l kärl - viktavgift färgat och ofärgat test</t>
         </is>
       </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
       <c r="M276" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N276" t="inlineStr"/>
       <c r="O276" t="inlineStr">
         <is>
           <t>X</t>
@@ -21560,16 +20699,11 @@
           <t>240 kärl/4 test metallförp textil</t>
         </is>
       </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
       <c r="M277" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N277" t="inlineStr"/>
       <c r="O277" t="inlineStr">
         <is>
           <t>X</t>
@@ -21627,16 +20761,11 @@
           <t>240 l kärl viktavg metallförp textil TEST</t>
         </is>
       </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
       <c r="M278" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N278" t="inlineStr"/>
       <c r="O278" t="inlineStr">
         <is>
           <t>X</t>
@@ -21694,16 +20823,11 @@
           <t>370 I Kärl/14 dgr TEST papper plast</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
       <c r="M279" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N279" t="inlineStr"/>
       <c r="O279" t="inlineStr">
         <is>
           <t>X</t>
@@ -21761,16 +20885,11 @@
           <t>370 I Kärl - viktavgift papper och plast TEST</t>
         </is>
       </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
       <c r="M280" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N280" t="inlineStr"/>
       <c r="O280" t="inlineStr">
         <is>
           <t>X</t>
@@ -21828,8 +20947,6 @@
           <t>Budad hämtning, trädgårdsavfall. Pris per m³</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -21845,7 +20962,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N281" t="inlineStr"/>
       <c r="O281" t="inlineStr">
         <is>
           <t>-</t>
@@ -21903,8 +21019,6 @@
           <t>Trädgårdsavfall, ris och stubbar till krossning</t>
         </is>
       </c>
-      <c r="I282" t="inlineStr"/>
-      <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
           <t>3200.0</t>
@@ -21920,7 +21034,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N282" t="inlineStr"/>
       <c r="O282" t="inlineStr">
         <is>
           <t>-</t>
@@ -21978,8 +21091,6 @@
           <t>Trädgårdsavfall komposterbart</t>
         </is>
       </c>
-      <c r="I283" t="inlineStr"/>
-      <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -21995,7 +21106,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N283" t="inlineStr"/>
       <c r="O283" t="inlineStr">
         <is>
           <t>-</t>
@@ -22053,8 +21163,6 @@
           <t>Tändare</t>
         </is>
       </c>
-      <c r="I284" t="inlineStr"/>
-      <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
           <t>120.0</t>
@@ -22070,7 +21178,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N284" t="inlineStr"/>
       <c r="O284" t="inlineStr">
         <is>
           <t>-</t>
@@ -22128,8 +21235,6 @@
           <t>Evenemangskärl 140 L, matavfall</t>
         </is>
       </c>
-      <c r="I285" t="inlineStr"/>
-      <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
           <t>96.0</t>
@@ -22145,7 +21250,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N285" t="inlineStr"/>
       <c r="O285" t="inlineStr">
         <is>
           <t>-</t>
@@ -22203,8 +21307,6 @@
           <t>Tömningar container, matavfall</t>
         </is>
       </c>
-      <c r="I286" t="inlineStr"/>
-      <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
           <t>440.0</t>
@@ -22220,7 +21322,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N286" t="inlineStr"/>
       <c r="O286" t="inlineStr">
         <is>
           <t>-</t>
@@ -22278,8 +21379,6 @@
           <t>Tömningar container, restavfall</t>
         </is>
       </c>
-      <c r="I287" t="inlineStr"/>
-      <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
           <t>440.0</t>
@@ -22295,7 +21394,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N287" t="inlineStr"/>
       <c r="O287" t="inlineStr">
         <is>
           <t>-</t>
@@ -22353,8 +21451,6 @@
           <t>Tömningar underjordsbehållare, matavfall</t>
         </is>
       </c>
-      <c r="I288" t="inlineStr"/>
-      <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
           <t>440.0</t>
@@ -22370,7 +21466,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N288" t="inlineStr"/>
       <c r="O288" t="inlineStr">
         <is>
           <t>-</t>
@@ -22428,8 +21523,6 @@
           <t>Tömningar underjordsbehållare, restavfall</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr"/>
-      <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
           <t>440.0</t>
@@ -22445,7 +21538,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N289" t="inlineStr"/>
       <c r="O289" t="inlineStr">
         <is>
           <t>-</t>
@@ -22503,8 +21595,6 @@
           <t>Tjänsttaxa underjordsbehållare för matavfall</t>
         </is>
       </c>
-      <c r="I290" t="inlineStr"/>
-      <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -22520,7 +21610,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N290" t="inlineStr"/>
       <c r="O290" t="inlineStr">
         <is>
           <t>-</t>
@@ -22578,8 +21667,6 @@
           <t>Tjänsttaxa underjordsbehållare för restavfall</t>
         </is>
       </c>
-      <c r="I291" t="inlineStr"/>
-      <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -22595,7 +21682,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N291" t="inlineStr"/>
       <c r="O291" t="inlineStr">
         <is>
           <t>-</t>
@@ -22633,7 +21719,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
           <t>1</t>
@@ -22649,8 +21734,6 @@
           <t>Undersökning av vattenmätare</t>
         </is>
       </c>
-      <c r="I292" t="inlineStr"/>
-      <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
           <t>960.0</t>
@@ -22666,7 +21749,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N292" t="inlineStr"/>
       <c r="O292" t="inlineStr">
         <is>
           <t>-</t>
@@ -22704,7 +21786,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
         <is>
           <t>1</t>
@@ -22720,8 +21801,6 @@
           <t>Uppsättning VA-mätare</t>
         </is>
       </c>
-      <c r="I293" t="inlineStr"/>
-      <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr">
         <is>
           <t>960.0</t>
@@ -22737,7 +21816,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N293" t="inlineStr"/>
       <c r="O293" t="inlineStr">
         <is>
           <t>-</t>
@@ -22795,8 +21873,6 @@
           <t>Grundavgift VA</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr"/>
-      <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr">
         <is>
           <t>776.16</t>
@@ -22812,7 +21888,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N294" t="inlineStr"/>
       <c r="O294" t="inlineStr">
         <is>
           <t>-</t>
@@ -22823,7 +21898,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -22866,8 +21940,6 @@
           <t>Avgift per m³ levererat vatten</t>
         </is>
       </c>
-      <c r="I295" t="inlineStr"/>
-      <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
           <t>18.42</t>
@@ -22883,7 +21955,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N295" t="inlineStr"/>
       <c r="O295" t="inlineStr">
         <is>
           <t>-</t>
@@ -22894,7 +21965,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -22937,8 +22007,6 @@
           <t>Bostadsenhetsavgift</t>
         </is>
       </c>
-      <c r="I296" t="inlineStr"/>
-      <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
           <t>1132.1</t>
@@ -22954,7 +22022,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N296" t="inlineStr"/>
       <c r="O296" t="inlineStr">
         <is>
           <t>-</t>
@@ -23012,8 +22079,6 @@
           <t>Avgift per påbörjad 150-tal m² bruttoarea</t>
         </is>
       </c>
-      <c r="I297" t="inlineStr"/>
-      <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr">
         <is>
           <t>1132.1</t>
@@ -23029,7 +22094,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N297" t="inlineStr"/>
       <c r="O297" t="inlineStr">
         <is>
           <t>-</t>
@@ -23087,8 +22151,6 @@
           <t>Vattenhaltiga blandningar av glykol, olja m.m</t>
         </is>
       </c>
-      <c r="I298" t="inlineStr"/>
-      <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
           <t>15.0</t>
@@ -23104,7 +22166,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N298" t="inlineStr"/>
       <c r="O298" t="inlineStr">
         <is>
           <t>-</t>
@@ -23162,8 +22223,6 @@
           <t>Grundavgift VA</t>
         </is>
       </c>
-      <c r="I299" t="inlineStr"/>
-      <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr">
         <is>
           <t>776.16</t>
@@ -23179,7 +22238,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N299" t="inlineStr"/>
       <c r="O299" t="inlineStr">
         <is>
           <t>-</t>
@@ -23190,7 +22248,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -23233,8 +22290,6 @@
           <t>Avgift per m³ levererat vatten</t>
         </is>
       </c>
-      <c r="I300" t="inlineStr"/>
-      <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr">
         <is>
           <t>18.42</t>
@@ -23250,7 +22305,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N300" t="inlineStr"/>
       <c r="O300" t="inlineStr">
         <is>
           <t>-</t>
@@ -23261,7 +22315,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -23304,8 +22357,6 @@
           <t>Bostadsenhetsavgift</t>
         </is>
       </c>
-      <c r="I301" t="inlineStr"/>
-      <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
           <t>1132.1</t>
@@ -23321,7 +22372,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N301" t="inlineStr"/>
       <c r="O301" t="inlineStr">
         <is>
           <t>-</t>
@@ -23379,8 +22429,6 @@
           <t>Bostadsenhetsavgift per påbörjad 150-tal m² bruttoarea</t>
         </is>
       </c>
-      <c r="I302" t="inlineStr"/>
-      <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr">
         <is>
           <t>1132.1</t>
@@ -23396,7 +22444,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N302" t="inlineStr"/>
       <c r="O302" t="inlineStr">
         <is>
           <t>-</t>
@@ -23454,8 +22501,6 @@
           <t>Avgift per m³ levererat vatten</t>
         </is>
       </c>
-      <c r="I303" t="inlineStr"/>
-      <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr">
         <is>
           <t>18.42</t>
@@ -23471,7 +22516,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N303" t="inlineStr"/>
       <c r="O303" t="inlineStr">
         <is>
           <t>-</t>
@@ -23482,7 +22526,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -23525,8 +22568,6 @@
           <t>Viktavgift matavfall</t>
         </is>
       </c>
-      <c r="I304" t="inlineStr"/>
-      <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -23542,7 +22583,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N304" t="inlineStr"/>
       <c r="O304" t="inlineStr">
         <is>
           <t>-</t>
@@ -23600,8 +22640,6 @@
           <t>Överviktsavgift för vikt över 60 kg, matavfall</t>
         </is>
       </c>
-      <c r="I305" t="inlineStr"/>
-      <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr">
         <is>
           <t>5.6</t>
@@ -23617,7 +22655,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N305" t="inlineStr"/>
       <c r="O305" t="inlineStr">
         <is>
           <t>-</t>
@@ -23675,8 +22712,6 @@
           <t>Viktavgift matavfall</t>
         </is>
       </c>
-      <c r="I306" t="inlineStr"/>
-      <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -23692,7 +22727,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N306" t="inlineStr"/>
       <c r="O306" t="inlineStr">
         <is>
           <t>-</t>
@@ -23750,8 +22784,6 @@
           <t>Viktavgift matavfall</t>
         </is>
       </c>
-      <c r="I307" t="inlineStr"/>
-      <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -23767,7 +22799,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N307" t="inlineStr"/>
       <c r="O307" t="inlineStr">
         <is>
           <t>-</t>
@@ -23825,8 +22856,6 @@
           <t>Viktavgift avfall reducerad taxa vid 1 lyft</t>
         </is>
       </c>
-      <c r="I308" t="inlineStr"/>
-      <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -23842,7 +22871,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N308" t="inlineStr"/>
       <c r="O308" t="inlineStr">
         <is>
           <t>-</t>
@@ -23900,8 +22928,6 @@
           <t>Överviktsavgift för vikt över 80 kg, Ospecifiserat avfall</t>
         </is>
       </c>
-      <c r="I309" t="inlineStr"/>
-      <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr">
         <is>
           <t>5.6</t>
@@ -23917,7 +22943,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N309" t="inlineStr"/>
       <c r="O309" t="inlineStr">
         <is>
           <t>-</t>
@@ -23975,8 +23000,6 @@
           <t>Viktavgift restavfall</t>
         </is>
       </c>
-      <c r="I310" t="inlineStr"/>
-      <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr">
         <is>
           <t>4.28</t>
@@ -23992,7 +23015,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N310" t="inlineStr"/>
       <c r="O310" t="inlineStr">
         <is>
           <t>-</t>
@@ -24050,8 +23072,6 @@
           <t>Överviktsavgift för vikt över 60 kg, restavfall</t>
         </is>
       </c>
-      <c r="I311" t="inlineStr"/>
-      <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr">
         <is>
           <t>5.6</t>
@@ -24067,7 +23087,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N311" t="inlineStr"/>
       <c r="O311" t="inlineStr">
         <is>
           <t>-</t>
@@ -24125,8 +23144,6 @@
           <t>Viktavgift restavfall</t>
         </is>
       </c>
-      <c r="I312" t="inlineStr"/>
-      <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
           <t>4.28</t>
@@ -24142,7 +23159,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N312" t="inlineStr"/>
       <c r="O312" t="inlineStr">
         <is>
           <t>-</t>
@@ -24180,7 +23196,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
           <t>1</t>
@@ -24196,16 +23211,11 @@
           <t>Dummytaxa för tjänst</t>
         </is>
       </c>
-      <c r="I313" t="inlineStr"/>
-      <c r="J313" t="inlineStr"/>
-      <c r="K313" t="inlineStr"/>
-      <c r="L313" t="inlineStr"/>
       <c r="M313" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N313" t="inlineStr"/>
       <c r="O313" t="inlineStr">
         <is>
           <t>-</t>
@@ -24216,7 +23226,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -24259,8 +23268,6 @@
           <t>Fast avgift vatten/spillvatten</t>
         </is>
       </c>
-      <c r="I314" t="inlineStr"/>
-      <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
           <t>1584.0</t>
@@ -24276,7 +23283,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N314" t="inlineStr"/>
       <c r="O314" t="inlineStr">
         <is>
           <t>-</t>
@@ -24287,7 +23293,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -24330,8 +23335,6 @@
           <t>Rörlig avgift, förbrukning per m³</t>
         </is>
       </c>
-      <c r="I315" t="inlineStr"/>
-      <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr">
         <is>
           <t>37.6</t>
@@ -24347,7 +23350,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N315" t="inlineStr"/>
       <c r="O315" t="inlineStr">
         <is>
           <t>-</t>
@@ -24358,7 +23360,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -24401,8 +23402,6 @@
           <t>Bostadsenhetsavgift VA</t>
         </is>
       </c>
-      <c r="I316" t="inlineStr"/>
-      <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
           <t>2310.4</t>
@@ -24418,7 +23417,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N316" t="inlineStr"/>
       <c r="O316" t="inlineStr">
         <is>
           <t>-</t>
@@ -24476,8 +23474,6 @@
           <t>Avgift per påbörjad 150-tal m² bruttoarea</t>
         </is>
       </c>
-      <c r="I317" t="inlineStr"/>
-      <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr">
         <is>
           <t>2310.4</t>
@@ -24493,7 +23489,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N317" t="inlineStr"/>
       <c r="O317" t="inlineStr">
         <is>
           <t>-</t>
@@ -24551,8 +23546,6 @@
           <t>Grundavgift + Bostadsenhetsavgift VA</t>
         </is>
       </c>
-      <c r="I318" t="inlineStr"/>
-      <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr">
         <is>
           <t>3894.0</t>
@@ -24568,7 +23561,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N318" t="inlineStr"/>
       <c r="O318" t="inlineStr">
         <is>
           <t>-</t>
@@ -24579,7 +23571,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -24622,8 +23613,6 @@
           <t>Grundavgift VA</t>
         </is>
       </c>
-      <c r="I319" t="inlineStr"/>
-      <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
           <t>1584.0</t>
@@ -24639,7 +23628,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N319" t="inlineStr"/>
       <c r="O319" t="inlineStr">
         <is>
           <t>-</t>
@@ -24650,7 +23638,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -24693,8 +23680,6 @@
           <t>Rörlig avgift, förbrukning per m³</t>
         </is>
       </c>
-      <c r="I320" t="inlineStr"/>
-      <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr">
         <is>
           <t>37.6</t>
@@ -24710,7 +23695,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N320" t="inlineStr"/>
       <c r="O320" t="inlineStr">
         <is>
           <t>-</t>
@@ -24721,7 +23705,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -24764,8 +23747,6 @@
           <t>Bostadsenhetsavgift VA</t>
         </is>
       </c>
-      <c r="I321" t="inlineStr"/>
-      <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
           <t>2310.4</t>
@@ -24781,7 +23762,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N321" t="inlineStr"/>
       <c r="O321" t="inlineStr">
         <is>
           <t>-</t>
@@ -24839,8 +23819,6 @@
           <t>Bostadsenhetsavgift per påbörjad 150-tal m² bruttoarea</t>
         </is>
       </c>
-      <c r="I322" t="inlineStr"/>
-      <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
           <t>2310.4</t>
@@ -24856,7 +23834,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N322" t="inlineStr"/>
       <c r="O322" t="inlineStr">
         <is>
           <t>-</t>
@@ -24914,8 +23891,6 @@
           <t>Endast förbrukning vatten/spillvatten</t>
         </is>
       </c>
-      <c r="I323" t="inlineStr"/>
-      <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr">
         <is>
           <t>37.6</t>
@@ -24931,7 +23906,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N323" t="inlineStr"/>
       <c r="O323" t="inlineStr">
         <is>
           <t>-</t>
@@ -24942,7 +23916,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -24965,7 +23938,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
         <is>
           <t>1</t>
@@ -24981,16 +23953,11 @@
           <t>Korrigering av händelse, konto och pris sätts manuellt</t>
         </is>
       </c>
-      <c r="I324" t="inlineStr"/>
-      <c r="J324" t="inlineStr"/>
-      <c r="K324" t="inlineStr"/>
-      <c r="L324" t="inlineStr"/>
       <c r="M324" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N324" t="inlineStr"/>
       <c r="O324" t="inlineStr">
         <is>
           <t>-</t>
@@ -25001,7 +23968,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -25044,8 +24010,6 @@
           <t>Total årskostnad för sommarvatten per Fritidshus maj-sept</t>
         </is>
       </c>
-      <c r="I325" t="inlineStr"/>
-      <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
           <t>1600.0</t>
@@ -25061,7 +24025,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N325" t="inlineStr"/>
       <c r="O325" t="inlineStr">
         <is>
           <t>-</t>
@@ -25119,8 +24082,6 @@
           <t>Grundavgift + Bostadsenhetsavgift VA</t>
         </is>
       </c>
-      <c r="I326" t="inlineStr"/>
-      <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
           <t>3894.0</t>
@@ -25136,7 +24097,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N326" t="inlineStr"/>
       <c r="O326" t="inlineStr">
         <is>
           <t>-</t>
@@ -25147,7 +24107,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -25190,8 +24149,6 @@
           <t>Rörlig avgift, uppsk. förbrukning per m³</t>
         </is>
       </c>
-      <c r="I327" t="inlineStr"/>
-      <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
           <t>37.6</t>
@@ -25207,7 +24164,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N327" t="inlineStr"/>
       <c r="O327" t="inlineStr">
         <is>
           <t>-</t>
@@ -25218,7 +24174,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -25261,8 +24216,6 @@
           <t>Grundavgift VA</t>
         </is>
       </c>
-      <c r="I328" t="inlineStr"/>
-      <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
           <t>1584.0</t>
@@ -25278,7 +24231,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N328" t="inlineStr"/>
       <c r="O328" t="inlineStr">
         <is>
           <t>-</t>
@@ -25289,7 +24241,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -25332,8 +24283,6 @@
           <t>Rörlig avgift, uppsk. förbrukning per m³</t>
         </is>
       </c>
-      <c r="I329" t="inlineStr"/>
-      <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr">
         <is>
           <t>37.6</t>
@@ -25349,7 +24298,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N329" t="inlineStr"/>
       <c r="O329" t="inlineStr">
         <is>
           <t>-</t>
@@ -25360,7 +24308,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -25403,8 +24350,6 @@
           <t>Bostadsenhetsavgift VA</t>
         </is>
       </c>
-      <c r="I330" t="inlineStr"/>
-      <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
           <t>2310.4</t>
@@ -25420,7 +24365,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N330" t="inlineStr"/>
       <c r="O330" t="inlineStr">
         <is>
           <t>-</t>
@@ -25478,8 +24422,6 @@
           <t>Bostadsenhetsavgift, per påbörjad 150-tal m² bruttoarea</t>
         </is>
       </c>
-      <c r="I331" t="inlineStr"/>
-      <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr">
         <is>
           <t>2310.4</t>
@@ -25495,7 +24437,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N331" t="inlineStr"/>
       <c r="O331" t="inlineStr">
         <is>
           <t>-</t>
@@ -25553,8 +24494,6 @@
           <t>Grundavgift VA</t>
         </is>
       </c>
-      <c r="I332" t="inlineStr"/>
-      <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr">
         <is>
           <t>1584.0</t>
@@ -25570,7 +24509,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N332" t="inlineStr"/>
       <c r="O332" t="inlineStr">
         <is>
           <t>-</t>
@@ -25581,7 +24519,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -25624,8 +24561,6 @@
           <t>Rörlig avgift uppskattad förbrukning per m³</t>
         </is>
       </c>
-      <c r="I333" t="inlineStr"/>
-      <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr">
         <is>
           <t>37.6</t>
@@ -25641,7 +24576,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N333" t="inlineStr"/>
       <c r="O333" t="inlineStr">
         <is>
           <t>-</t>
@@ -25652,7 +24586,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -25695,8 +24628,6 @@
           <t>Bostadsenhetsavgift per bostadsenhet VA</t>
         </is>
       </c>
-      <c r="I334" t="inlineStr"/>
-      <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr">
         <is>
           <t>2310.4</t>
@@ -25712,7 +24643,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N334" t="inlineStr"/>
       <c r="O334" t="inlineStr">
         <is>
           <t>-</t>
@@ -25770,8 +24700,6 @@
           <t>Avgift per påbörjad 150-tal m² bruttoarea</t>
         </is>
       </c>
-      <c r="I335" t="inlineStr"/>
-      <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr">
         <is>
           <t>2310.4</t>
@@ -25787,7 +24715,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N335" t="inlineStr"/>
       <c r="O335" t="inlineStr">
         <is>
           <t>-</t>
@@ -25845,8 +24772,6 @@
           <t>Grundavgift VA och Bostadsenhetsavgift</t>
         </is>
       </c>
-      <c r="I336" t="inlineStr"/>
-      <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
           <t>1908.26</t>
@@ -25862,7 +24787,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N336" t="inlineStr"/>
       <c r="O336" t="inlineStr">
         <is>
           <t>-</t>
@@ -25873,7 +24797,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -25916,8 +24839,6 @@
           <t>Rörlig avgift, uppsk. förbrukning per m³</t>
         </is>
       </c>
-      <c r="I337" t="inlineStr"/>
-      <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr">
         <is>
           <t>18.42</t>
@@ -25933,7 +24854,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N337" t="inlineStr"/>
       <c r="O337" t="inlineStr">
         <is>
           <t>-</t>
@@ -25944,7 +24864,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -25987,8 +24906,6 @@
           <t>Grundavgift VA</t>
         </is>
       </c>
-      <c r="I338" t="inlineStr"/>
-      <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr">
         <is>
           <t>776.16</t>
@@ -26004,7 +24921,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N338" t="inlineStr"/>
       <c r="O338" t="inlineStr">
         <is>
           <t>-</t>
@@ -26015,7 +24931,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -26058,8 +24973,6 @@
           <t>Rörlig avgift, uppsk. förbrukning per m³</t>
         </is>
       </c>
-      <c r="I339" t="inlineStr"/>
-      <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr">
         <is>
           <t>18.42</t>
@@ -26075,7 +24988,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N339" t="inlineStr"/>
       <c r="O339" t="inlineStr">
         <is>
           <t>-</t>
@@ -26086,7 +24998,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -26129,8 +25040,6 @@
           <t>Bostadsenhetsavgift</t>
         </is>
       </c>
-      <c r="I340" t="inlineStr"/>
-      <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr">
         <is>
           <t>1132.1</t>
@@ -26146,7 +25055,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N340" t="inlineStr"/>
       <c r="O340" t="inlineStr">
         <is>
           <t>-</t>
@@ -26204,8 +25112,6 @@
           <t>Bostadsenhetsavgift, per påbörjad 150 m² BTA</t>
         </is>
       </c>
-      <c r="I341" t="inlineStr"/>
-      <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr">
         <is>
           <t>1132.1</t>
@@ -26221,7 +25127,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N341" t="inlineStr"/>
       <c r="O341" t="inlineStr">
         <is>
           <t>-</t>
@@ -26279,8 +25184,6 @@
           <t>Grundavgift + Bostadsenhetsavgift VA</t>
         </is>
       </c>
-      <c r="I342" t="inlineStr"/>
-      <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr">
         <is>
           <t>1908.26</t>
@@ -26296,7 +25199,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N342" t="inlineStr"/>
       <c r="O342" t="inlineStr">
         <is>
           <t>-</t>
@@ -26307,7 +25209,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -26350,8 +25251,6 @@
           <t>Rörlig avgift, uppsk. förbrukning per m³</t>
         </is>
       </c>
-      <c r="I343" t="inlineStr"/>
-      <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr">
         <is>
           <t>18.42</t>
@@ -26367,7 +25266,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N343" t="inlineStr"/>
       <c r="O343" t="inlineStr">
         <is>
           <t>-</t>
@@ -26378,7 +25276,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -26421,16 +25318,11 @@
           <t>ÅVS behandling glasförpackningar, färgade</t>
         </is>
       </c>
-      <c r="I344" t="inlineStr"/>
-      <c r="J344" t="inlineStr"/>
-      <c r="K344" t="inlineStr"/>
-      <c r="L344" t="inlineStr"/>
       <c r="M344" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N344" t="inlineStr"/>
       <c r="O344" t="inlineStr">
         <is>
           <t>-</t>
@@ -26488,16 +25380,11 @@
           <t>ÅVS behandling glasförpackningar, ofärgade</t>
         </is>
       </c>
-      <c r="I345" t="inlineStr"/>
-      <c r="J345" t="inlineStr"/>
-      <c r="K345" t="inlineStr"/>
-      <c r="L345" t="inlineStr"/>
       <c r="M345" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N345" t="inlineStr"/>
       <c r="O345" t="inlineStr">
         <is>
           <t>-</t>
@@ -26555,16 +25442,11 @@
           <t>ÅVS behandling matavfall</t>
         </is>
       </c>
-      <c r="I346" t="inlineStr"/>
-      <c r="J346" t="inlineStr"/>
-      <c r="K346" t="inlineStr"/>
-      <c r="L346" t="inlineStr"/>
       <c r="M346" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N346" t="inlineStr"/>
       <c r="O346" t="inlineStr">
         <is>
           <t>-</t>
@@ -26622,16 +25504,11 @@
           <t>ÅVS behandling metallförpackningar</t>
         </is>
       </c>
-      <c r="I347" t="inlineStr"/>
-      <c r="J347" t="inlineStr"/>
-      <c r="K347" t="inlineStr"/>
-      <c r="L347" t="inlineStr"/>
       <c r="M347" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N347" t="inlineStr"/>
       <c r="O347" t="inlineStr">
         <is>
           <t>-</t>
@@ -26689,16 +25566,11 @@
           <t>ÅVS behandling pappersförpackningar</t>
         </is>
       </c>
-      <c r="I348" t="inlineStr"/>
-      <c r="J348" t="inlineStr"/>
-      <c r="K348" t="inlineStr"/>
-      <c r="L348" t="inlineStr"/>
       <c r="M348" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N348" t="inlineStr"/>
       <c r="O348" t="inlineStr">
         <is>
           <t>-</t>
@@ -26756,16 +25628,11 @@
           <t>ÅVS behandling plastförpackningar</t>
         </is>
       </c>
-      <c r="I349" t="inlineStr"/>
-      <c r="J349" t="inlineStr"/>
-      <c r="K349" t="inlineStr"/>
-      <c r="L349" t="inlineStr"/>
       <c r="M349" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N349" t="inlineStr"/>
       <c r="O349" t="inlineStr">
         <is>
           <t>-</t>
@@ -26823,16 +25690,11 @@
           <t>ÅVS behandling restavfall</t>
         </is>
       </c>
-      <c r="I350" t="inlineStr"/>
-      <c r="J350" t="inlineStr"/>
-      <c r="K350" t="inlineStr"/>
-      <c r="L350" t="inlineStr"/>
       <c r="M350" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N350" t="inlineStr"/>
       <c r="O350" t="inlineStr">
         <is>
           <t>-</t>
@@ -26890,16 +25752,11 @@
           <t>ÅVS behandling tidningar</t>
         </is>
       </c>
-      <c r="I351" t="inlineStr"/>
-      <c r="J351" t="inlineStr"/>
-      <c r="K351" t="inlineStr"/>
-      <c r="L351" t="inlineStr"/>
       <c r="M351" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N351" t="inlineStr"/>
       <c r="O351" t="inlineStr">
         <is>
           <t>-</t>
@@ -26957,16 +25814,11 @@
           <t>ÅVS metallförpackningar. Tjänsttaxa</t>
         </is>
       </c>
-      <c r="I352" t="inlineStr"/>
-      <c r="J352" t="inlineStr"/>
-      <c r="K352" t="inlineStr"/>
-      <c r="L352" t="inlineStr"/>
       <c r="M352" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N352" t="inlineStr"/>
       <c r="O352" t="inlineStr">
         <is>
           <t>-</t>
@@ -27024,16 +25876,11 @@
           <t>ÅVS tömning, glasförpackningar, färgade</t>
         </is>
       </c>
-      <c r="I353" t="inlineStr"/>
-      <c r="J353" t="inlineStr"/>
-      <c r="K353" t="inlineStr"/>
-      <c r="L353" t="inlineStr"/>
       <c r="M353" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N353" t="inlineStr"/>
       <c r="O353" t="inlineStr">
         <is>
           <t>-</t>
@@ -27091,16 +25938,11 @@
           <t>ÅVS tömning glasförpackningar, ofärgade</t>
         </is>
       </c>
-      <c r="I354" t="inlineStr"/>
-      <c r="J354" t="inlineStr"/>
-      <c r="K354" t="inlineStr"/>
-      <c r="L354" t="inlineStr"/>
       <c r="M354" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N354" t="inlineStr"/>
       <c r="O354" t="inlineStr">
         <is>
           <t>-</t>
@@ -27158,16 +26000,11 @@
           <t>ÅVS tömning matavfall</t>
         </is>
       </c>
-      <c r="I355" t="inlineStr"/>
-      <c r="J355" t="inlineStr"/>
-      <c r="K355" t="inlineStr"/>
-      <c r="L355" t="inlineStr"/>
       <c r="M355" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N355" t="inlineStr"/>
       <c r="O355" t="inlineStr">
         <is>
           <t>-</t>
@@ -27225,16 +26062,11 @@
           <t>ÅVS tömning metallförpackningar</t>
         </is>
       </c>
-      <c r="I356" t="inlineStr"/>
-      <c r="J356" t="inlineStr"/>
-      <c r="K356" t="inlineStr"/>
-      <c r="L356" t="inlineStr"/>
       <c r="M356" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N356" t="inlineStr"/>
       <c r="O356" t="inlineStr">
         <is>
           <t>-</t>
@@ -27292,16 +26124,11 @@
           <t>ÅVS tömning pappersförpackningar</t>
         </is>
       </c>
-      <c r="I357" t="inlineStr"/>
-      <c r="J357" t="inlineStr"/>
-      <c r="K357" t="inlineStr"/>
-      <c r="L357" t="inlineStr"/>
       <c r="M357" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N357" t="inlineStr"/>
       <c r="O357" t="inlineStr">
         <is>
           <t>-</t>
@@ -27359,16 +26186,11 @@
           <t>ÅVS tömning plastförpackningar</t>
         </is>
       </c>
-      <c r="I358" t="inlineStr"/>
-      <c r="J358" t="inlineStr"/>
-      <c r="K358" t="inlineStr"/>
-      <c r="L358" t="inlineStr"/>
       <c r="M358" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N358" t="inlineStr"/>
       <c r="O358" t="inlineStr">
         <is>
           <t>-</t>
@@ -27426,16 +26248,11 @@
           <t>ÅVS tömning restavfall</t>
         </is>
       </c>
-      <c r="I359" t="inlineStr"/>
-      <c r="J359" t="inlineStr"/>
-      <c r="K359" t="inlineStr"/>
-      <c r="L359" t="inlineStr"/>
       <c r="M359" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N359" t="inlineStr"/>
       <c r="O359" t="inlineStr">
         <is>
           <t>-</t>
@@ -27493,16 +26310,11 @@
           <t>ÅVS tömning tidningar</t>
         </is>
       </c>
-      <c r="I360" t="inlineStr"/>
-      <c r="J360" t="inlineStr"/>
-      <c r="K360" t="inlineStr"/>
-      <c r="L360" t="inlineStr"/>
       <c r="M360" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N360" t="inlineStr"/>
       <c r="O360" t="inlineStr">
         <is>
           <t>-</t>
@@ -27560,8 +26372,6 @@
           <t>Kärl 660 Invasiva arter</t>
         </is>
       </c>
-      <c r="I361" t="inlineStr"/>
-      <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -27577,7 +26387,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N361" t="inlineStr"/>
       <c r="O361" t="inlineStr">
         <is>
           <t>-</t>
@@ -27635,8 +26444,6 @@
           <t>Kärl 660 Textil</t>
         </is>
       </c>
-      <c r="I362" t="inlineStr"/>
-      <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -27652,7 +26459,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N362" t="inlineStr"/>
       <c r="O362" t="inlineStr">
         <is>
           <t>-</t>
@@ -27690,7 +26496,6 @@
           <t>RENH</t>
         </is>
       </c>
-      <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
           <t>1</t>
@@ -27706,8 +26511,6 @@
           <t>ÅVC-abonnemang nivå 1 – ej miljöfarligt avfall</t>
         </is>
       </c>
-      <c r="I363" t="inlineStr"/>
-      <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr">
         <is>
           <t>1600.0</t>
@@ -27723,7 +26526,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N363" t="inlineStr"/>
       <c r="O363" t="inlineStr">
         <is>
           <t>-</t>
@@ -27761,7 +26563,6 @@
           <t>RENH</t>
         </is>
       </c>
-      <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
           <t>1</t>
@@ -27777,8 +26578,6 @@
           <t>ÅVC-abonnemang nivå 2 – med miljöfarligt avfall</t>
         </is>
       </c>
-      <c r="I364" t="inlineStr"/>
-      <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr">
         <is>
           <t>3200.0</t>
@@ -27794,7 +26593,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N364" t="inlineStr"/>
       <c r="O364" t="inlineStr">
         <is>
           <t>-</t>
@@ -27852,16 +26650,11 @@
           <t>Fyllnadsgrad</t>
         </is>
       </c>
-      <c r="I365" t="inlineStr"/>
-      <c r="J365" t="inlineStr"/>
-      <c r="K365" t="inlineStr"/>
-      <c r="L365" t="inlineStr"/>
       <c r="M365" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N365" t="inlineStr"/>
       <c r="O365" t="inlineStr">
         <is>
           <t>-</t>
@@ -27919,16 +26712,11 @@
           <t>ÅVS, glasförpackningar, färgade, Tjänsttaxa</t>
         </is>
       </c>
-      <c r="I366" t="inlineStr"/>
-      <c r="J366" t="inlineStr"/>
-      <c r="K366" t="inlineStr"/>
-      <c r="L366" t="inlineStr"/>
       <c r="M366" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N366" t="inlineStr"/>
       <c r="O366" t="inlineStr">
         <is>
           <t>-</t>
@@ -27986,16 +26774,11 @@
           <t>ÅVS glasförpackningar, ofärgade. Tjänsttaxa</t>
         </is>
       </c>
-      <c r="I367" t="inlineStr"/>
-      <c r="J367" t="inlineStr"/>
-      <c r="K367" t="inlineStr"/>
-      <c r="L367" t="inlineStr"/>
       <c r="M367" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N367" t="inlineStr"/>
       <c r="O367" t="inlineStr">
         <is>
           <t>-</t>
@@ -28053,16 +26836,11 @@
           <t>ÅVS matavfall. Tjänsttaxa</t>
         </is>
       </c>
-      <c r="I368" t="inlineStr"/>
-      <c r="J368" t="inlineStr"/>
-      <c r="K368" t="inlineStr"/>
-      <c r="L368" t="inlineStr"/>
       <c r="M368" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N368" t="inlineStr"/>
       <c r="O368" t="inlineStr">
         <is>
           <t>-</t>
@@ -28120,16 +26898,11 @@
           <t>ÅVS metallförpackningar. Tjänsttaxa</t>
         </is>
       </c>
-      <c r="I369" t="inlineStr"/>
-      <c r="J369" t="inlineStr"/>
-      <c r="K369" t="inlineStr"/>
-      <c r="L369" t="inlineStr"/>
       <c r="M369" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N369" t="inlineStr"/>
       <c r="O369" t="inlineStr">
         <is>
           <t>-</t>
@@ -28187,16 +26960,11 @@
           <t>ÅVS pappersförpackningar. Tjänsttaxa</t>
         </is>
       </c>
-      <c r="I370" t="inlineStr"/>
-      <c r="J370" t="inlineStr"/>
-      <c r="K370" t="inlineStr"/>
-      <c r="L370" t="inlineStr"/>
       <c r="M370" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N370" t="inlineStr"/>
       <c r="O370" t="inlineStr">
         <is>
           <t>-</t>
@@ -28254,16 +27022,11 @@
           <t>ÅVS plastförpackningar. Tjänsttaxa</t>
         </is>
       </c>
-      <c r="I371" t="inlineStr"/>
-      <c r="J371" t="inlineStr"/>
-      <c r="K371" t="inlineStr"/>
-      <c r="L371" t="inlineStr"/>
       <c r="M371" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N371" t="inlineStr"/>
       <c r="O371" t="inlineStr">
         <is>
           <t>-</t>
@@ -28321,16 +27084,11 @@
           <t>ÅVS restavfall. Tjänsttaxa</t>
         </is>
       </c>
-      <c r="I372" t="inlineStr"/>
-      <c r="J372" t="inlineStr"/>
-      <c r="K372" t="inlineStr"/>
-      <c r="L372" t="inlineStr"/>
       <c r="M372" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N372" t="inlineStr"/>
       <c r="O372" t="inlineStr">
         <is>
           <t>-</t>
@@ -28388,16 +27146,11 @@
           <t>ÅVS tidningar. Tjänsttaxa</t>
         </is>
       </c>
-      <c r="I373" t="inlineStr"/>
-      <c r="J373" t="inlineStr"/>
-      <c r="K373" t="inlineStr"/>
-      <c r="L373" t="inlineStr"/>
       <c r="M373" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N373" t="inlineStr"/>
       <c r="O373" t="inlineStr">
         <is>
           <t>-</t>
@@ -28564,7 +27317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -28677,35 +27430,6 @@
       <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Kommentar</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>EDP Standardtaxor / regelverk / manuell granskning</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Ej granskad</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>EDP-data får aldrig blandas mellan projekt.</t>
         </is>
       </c>
     </row>
@@ -28885,7 +27609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -28992,46 +27716,6 @@
       <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Kommentar</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Taxakod</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Ej satt</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Befintlig Taxa_från_edp är fast. Standardtaxor får endast ge förslag/avvikelse.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Regelverk</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Ej granskad</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Standardflik för framtida spårning.</t>
         </is>
       </c>
     </row>
@@ -35617,7 +34301,6 @@
         </is>
       </c>
     </row>
-    <row r="216"/>
     <row r="217">
       <c r="D217" s="18" t="inlineStr">
         <is>
@@ -35778,7 +34461,6 @@
         </is>
       </c>
     </row>
-    <row r="222"/>
     <row r="223">
       <c r="D223" s="18" t="inlineStr">
         <is>
@@ -35939,7 +34621,6 @@
         </is>
       </c>
     </row>
-    <row r="228"/>
     <row r="229">
       <c r="D229" s="18" t="inlineStr">
         <is>
@@ -36100,7 +34781,6 @@
         </is>
       </c>
     </row>
-    <row r="234"/>
     <row r="235">
       <c r="D235" s="18" t="inlineStr">
         <is>
@@ -36261,7 +34941,6 @@
         </is>
       </c>
     </row>
-    <row r="240"/>
     <row r="241">
       <c r="D241" s="18" t="inlineStr">
         <is>
@@ -36422,7 +35101,6 @@
         </is>
       </c>
     </row>
-    <row r="246"/>
     <row r="247">
       <c r="D247" s="18" t="inlineStr">
         <is>
@@ -36583,7 +35261,6 @@
         </is>
       </c>
     </row>
-    <row r="252"/>
     <row r="253">
       <c r="D253" s="18" t="inlineStr">
         <is>
@@ -36744,7 +35421,6 @@
         </is>
       </c>
     </row>
-    <row r="258"/>
     <row r="259">
       <c r="D259" s="18" t="inlineStr">
         <is>
@@ -36905,7 +35581,6 @@
         </is>
       </c>
     </row>
-    <row r="264"/>
     <row r="265">
       <c r="D265" s="18" t="inlineStr">
         <is>
@@ -37066,7 +35741,6 @@
         </is>
       </c>
     </row>
-    <row r="270"/>
     <row r="271">
       <c r="D271" s="18" t="inlineStr">
         <is>
@@ -45843,7 +44517,6 @@
         </is>
       </c>
     </row>
-    <row r="113"/>
     <row r="114">
       <c r="A114" s="44" t="inlineStr">
         <is>
